--- a/outputs/daily/hr_rankings_2026-08-16_full.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-16_full.xlsx
@@ -2506,34 +2506,30 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -12854,34 +12850,30 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB45" t="inlineStr"/>
       <c r="AC45" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -13978,34 +13970,30 @@
       </c>
       <c r="W49" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB49" t="inlineStr"/>
       <c r="AC49" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -18162,34 +18150,30 @@
       </c>
       <c r="W64" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y64" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB64" t="inlineStr"/>
       <c r="AC64" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -32122,34 +32106,30 @@
       </c>
       <c r="W114" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X114" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X114" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y114" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z114" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB114" t="inlineStr"/>
       <c r="AC114" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -32406,34 +32386,30 @@
       </c>
       <c r="W115" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X115" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z115" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X115" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y115" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z115" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB115" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 8</t>
-        </is>
-      </c>
+      <c r="AB115" t="inlineStr"/>
       <c r="AC115" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -33522,34 +33498,30 @@
       </c>
       <c r="W119" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X119" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z119" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X119" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y119" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z119" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AB119" t="inlineStr"/>
       <c r="AC119" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -39640,28 +39612,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W141" t="inlineStr"/>
-      <c r="X141" t="inlineStr"/>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X141" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="Y141" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z141" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z141" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB141" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB141" t="inlineStr"/>
       <c r="AC141" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -39916,28 +39892,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W142" t="inlineStr"/>
-      <c r="X142" t="inlineStr"/>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X142" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="Y142" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z142" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z142" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA142" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB142" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB142" t="inlineStr"/>
       <c r="AC142" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -77932,34 +77912,30 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
